--- a/artfynd/A 41968-2025 artfynd.xlsx
+++ b/artfynd/A 41968-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,9 +804,136 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137350490</v>
+      </c>
+      <c r="B3" t="n">
+        <v>9424</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nornornas väg 43, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>540760</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6230503</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Augerum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor och fin levande hane.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137350490</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
